--- a/Media/Host.xlsx
+++ b/Media/Host.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milenia" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filiberto" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BAH Congreso" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baires" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Independencia" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procedimientos" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklists" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reservas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Milenia" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Filiberto" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BAH Congreso" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Baires" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Independencia" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Procedimientos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Checklists" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Reservas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>14D</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>8862</t>
         </is>
       </c>
     </row>
@@ -3645,12 +3645,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>14J</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>6017</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>14E</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>9225</t>
         </is>
       </c>
     </row>
@@ -3679,12 +3679,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>14F</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>8157</t>
         </is>
       </c>
     </row>
@@ -3696,12 +3696,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Extra</t>
+          <t>13E</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4559</t>
         </is>
       </c>
     </row>
@@ -3713,12 +3713,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Extra</t>
+          <t>13G</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>0401</t>
         </is>
       </c>
     </row>
@@ -3730,16 +3730,100 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>13H</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="8" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14H</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5283</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13F</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1786</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>14G</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>6481</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>14I</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="8" customHeight="1"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3623</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
@@ -4197,8 +4281,8 @@
   <mergeCells count="8">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
